--- a/backend/data/financials_by_company/002489.SZ.xlsx
+++ b/backend/data/financials_by_company/002489.SZ.xlsx
@@ -3498,7 +3498,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:EM2"/>
+  <dimension ref="A1:EN2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3529,690 +3529,695 @@
       </c>
       <c r="F1" t="inlineStr">
         <is>
+          <t>fax</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
           <t>website</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>industry</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>industryKey</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>industryDisp</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>sector</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>sectorKey</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>sectorDisp</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>longBusinessSummary</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>fullTimeEmployees</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>companyOfficers</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>executiveTeam</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>maxAge</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>priceHint</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>previousClose</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>open</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>dayLow</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>dayHigh</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>regularMarketPreviousClose</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="Y1" t="inlineStr">
         <is>
           <t>regularMarketOpen</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
         <is>
           <t>regularMarketDayLow</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="AA1" t="inlineStr">
         <is>
           <t>regularMarketDayHigh</t>
         </is>
       </c>
-      <c r="AA1" t="inlineStr">
+      <c r="AB1" t="inlineStr">
         <is>
           <t>dividendRate</t>
         </is>
       </c>
-      <c r="AB1" t="inlineStr">
+      <c r="AC1" t="inlineStr">
         <is>
           <t>dividendYield</t>
         </is>
       </c>
-      <c r="AC1" t="inlineStr">
+      <c r="AD1" t="inlineStr">
         <is>
           <t>exDividendDate</t>
         </is>
       </c>
-      <c r="AD1" t="inlineStr">
+      <c r="AE1" t="inlineStr">
         <is>
           <t>payoutRatio</t>
         </is>
       </c>
-      <c r="AE1" t="inlineStr">
+      <c r="AF1" t="inlineStr">
         <is>
           <t>fiveYearAvgDividendYield</t>
         </is>
       </c>
-      <c r="AF1" t="inlineStr">
+      <c r="AG1" t="inlineStr">
         <is>
           <t>beta</t>
         </is>
       </c>
-      <c r="AG1" t="inlineStr">
+      <c r="AH1" t="inlineStr">
         <is>
           <t>trailingPE</t>
         </is>
       </c>
-      <c r="AH1" t="inlineStr">
+      <c r="AI1" t="inlineStr">
         <is>
           <t>volume</t>
         </is>
       </c>
-      <c r="AI1" t="inlineStr">
+      <c r="AJ1" t="inlineStr">
         <is>
           <t>regularMarketVolume</t>
         </is>
       </c>
-      <c r="AJ1" t="inlineStr">
+      <c r="AK1" t="inlineStr">
         <is>
           <t>averageVolume</t>
         </is>
       </c>
-      <c r="AK1" t="inlineStr">
+      <c r="AL1" t="inlineStr">
         <is>
           <t>averageVolume10days</t>
         </is>
       </c>
-      <c r="AL1" t="inlineStr">
+      <c r="AM1" t="inlineStr">
         <is>
           <t>averageDailyVolume10Day</t>
         </is>
       </c>
-      <c r="AM1" t="inlineStr">
+      <c r="AN1" t="inlineStr">
         <is>
           <t>bid</t>
         </is>
       </c>
-      <c r="AN1" t="inlineStr">
+      <c r="AO1" t="inlineStr">
         <is>
           <t>ask</t>
         </is>
       </c>
-      <c r="AO1" t="inlineStr">
+      <c r="AP1" t="inlineStr">
         <is>
           <t>marketCap</t>
         </is>
       </c>
-      <c r="AP1" t="inlineStr">
+      <c r="AQ1" t="inlineStr">
         <is>
           <t>nonDilutedMarketCap</t>
         </is>
       </c>
-      <c r="AQ1" t="inlineStr">
+      <c r="AR1" t="inlineStr">
         <is>
           <t>fiftyTwoWeekLow</t>
         </is>
       </c>
-      <c r="AR1" t="inlineStr">
+      <c r="AS1" t="inlineStr">
         <is>
           <t>fiftyTwoWeekHigh</t>
         </is>
       </c>
-      <c r="AS1" t="inlineStr">
+      <c r="AT1" t="inlineStr">
         <is>
           <t>allTimeHigh</t>
         </is>
       </c>
-      <c r="AT1" t="inlineStr">
+      <c r="AU1" t="inlineStr">
         <is>
           <t>allTimeLow</t>
         </is>
       </c>
-      <c r="AU1" t="inlineStr">
+      <c r="AV1" t="inlineStr">
         <is>
           <t>priceToSalesTrailing12Months</t>
         </is>
       </c>
-      <c r="AV1" t="inlineStr">
+      <c r="AW1" t="inlineStr">
         <is>
           <t>fiftyDayAverage</t>
         </is>
       </c>
-      <c r="AW1" t="inlineStr">
+      <c r="AX1" t="inlineStr">
         <is>
           <t>twoHundredDayAverage</t>
         </is>
       </c>
-      <c r="AX1" t="inlineStr">
+      <c r="AY1" t="inlineStr">
         <is>
           <t>trailingAnnualDividendRate</t>
         </is>
       </c>
-      <c r="AY1" t="inlineStr">
+      <c r="AZ1" t="inlineStr">
         <is>
           <t>trailingAnnualDividendYield</t>
         </is>
       </c>
-      <c r="AZ1" t="inlineStr">
+      <c r="BA1" t="inlineStr">
         <is>
           <t>currency</t>
         </is>
       </c>
-      <c r="BA1" t="inlineStr">
+      <c r="BB1" t="inlineStr">
         <is>
           <t>tradeable</t>
         </is>
       </c>
-      <c r="BB1" t="inlineStr">
+      <c r="BC1" t="inlineStr">
         <is>
           <t>enterpriseValue</t>
         </is>
       </c>
-      <c r="BC1" t="inlineStr">
+      <c r="BD1" t="inlineStr">
         <is>
           <t>profitMargins</t>
         </is>
       </c>
-      <c r="BD1" t="inlineStr">
+      <c r="BE1" t="inlineStr">
         <is>
           <t>floatShares</t>
         </is>
       </c>
-      <c r="BE1" t="inlineStr">
+      <c r="BF1" t="inlineStr">
         <is>
           <t>sharesOutstanding</t>
         </is>
       </c>
-      <c r="BF1" t="inlineStr">
+      <c r="BG1" t="inlineStr">
         <is>
           <t>heldPercentInsiders</t>
         </is>
       </c>
-      <c r="BG1" t="inlineStr">
+      <c r="BH1" t="inlineStr">
         <is>
           <t>heldPercentInstitutions</t>
         </is>
       </c>
-      <c r="BH1" t="inlineStr">
+      <c r="BI1" t="inlineStr">
         <is>
           <t>impliedSharesOutstanding</t>
         </is>
       </c>
-      <c r="BI1" t="inlineStr">
+      <c r="BJ1" t="inlineStr">
         <is>
           <t>bookValue</t>
         </is>
       </c>
-      <c r="BJ1" t="inlineStr">
+      <c r="BK1" t="inlineStr">
         <is>
           <t>priceToBook</t>
         </is>
       </c>
-      <c r="BK1" t="inlineStr">
+      <c r="BL1" t="inlineStr">
         <is>
           <t>lastFiscalYearEnd</t>
         </is>
       </c>
-      <c r="BL1" t="inlineStr">
+      <c r="BM1" t="inlineStr">
         <is>
           <t>nextFiscalYearEnd</t>
         </is>
       </c>
-      <c r="BM1" t="inlineStr">
+      <c r="BN1" t="inlineStr">
         <is>
           <t>mostRecentQuarter</t>
         </is>
       </c>
-      <c r="BN1" t="inlineStr">
+      <c r="BO1" t="inlineStr">
         <is>
           <t>earningsQuarterlyGrowth</t>
         </is>
       </c>
-      <c r="BO1" t="inlineStr">
+      <c r="BP1" t="inlineStr">
         <is>
           <t>netIncomeToCommon</t>
         </is>
       </c>
-      <c r="BP1" t="inlineStr">
+      <c r="BQ1" t="inlineStr">
         <is>
           <t>trailingEps</t>
         </is>
       </c>
-      <c r="BQ1" t="inlineStr">
+      <c r="BR1" t="inlineStr">
         <is>
           <t>lastSplitFactor</t>
         </is>
       </c>
-      <c r="BR1" t="inlineStr">
+      <c r="BS1" t="inlineStr">
         <is>
           <t>lastSplitDate</t>
         </is>
       </c>
-      <c r="BS1" t="inlineStr">
+      <c r="BT1" t="inlineStr">
         <is>
           <t>enterpriseToRevenue</t>
         </is>
       </c>
-      <c r="BT1" t="inlineStr">
+      <c r="BU1" t="inlineStr">
         <is>
           <t>enterpriseToEbitda</t>
         </is>
       </c>
-      <c r="BU1" t="inlineStr">
+      <c r="BV1" t="inlineStr">
         <is>
           <t>52WeekChange</t>
         </is>
       </c>
-      <c r="BV1" t="inlineStr">
+      <c r="BW1" t="inlineStr">
         <is>
           <t>SandP52WeekChange</t>
         </is>
       </c>
-      <c r="BW1" t="inlineStr">
+      <c r="BX1" t="inlineStr">
         <is>
           <t>lastDividendValue</t>
         </is>
       </c>
-      <c r="BX1" t="inlineStr">
+      <c r="BY1" t="inlineStr">
         <is>
           <t>lastDividendDate</t>
         </is>
       </c>
-      <c r="BY1" t="inlineStr">
+      <c r="BZ1" t="inlineStr">
         <is>
           <t>quoteType</t>
         </is>
       </c>
-      <c r="BZ1" t="inlineStr">
+      <c r="CA1" t="inlineStr">
         <is>
           <t>currentPrice</t>
         </is>
       </c>
-      <c r="CA1" t="inlineStr">
+      <c r="CB1" t="inlineStr">
         <is>
           <t>recommendationKey</t>
         </is>
       </c>
-      <c r="CB1" t="inlineStr">
+      <c r="CC1" t="inlineStr">
         <is>
           <t>totalCash</t>
         </is>
       </c>
-      <c r="CC1" t="inlineStr">
+      <c r="CD1" t="inlineStr">
         <is>
           <t>totalCashPerShare</t>
         </is>
       </c>
-      <c r="CD1" t="inlineStr">
+      <c r="CE1" t="inlineStr">
         <is>
           <t>ebitda</t>
         </is>
       </c>
-      <c r="CE1" t="inlineStr">
+      <c r="CF1" t="inlineStr">
         <is>
           <t>totalDebt</t>
         </is>
       </c>
-      <c r="CF1" t="inlineStr">
+      <c r="CG1" t="inlineStr">
         <is>
           <t>quickRatio</t>
         </is>
       </c>
-      <c r="CG1" t="inlineStr">
+      <c r="CH1" t="inlineStr">
         <is>
           <t>currentRatio</t>
         </is>
       </c>
-      <c r="CH1" t="inlineStr">
+      <c r="CI1" t="inlineStr">
         <is>
           <t>totalRevenue</t>
         </is>
       </c>
-      <c r="CI1" t="inlineStr">
+      <c r="CJ1" t="inlineStr">
         <is>
           <t>debtToEquity</t>
         </is>
       </c>
-      <c r="CJ1" t="inlineStr">
+      <c r="CK1" t="inlineStr">
         <is>
           <t>revenuePerShare</t>
         </is>
       </c>
-      <c r="CK1" t="inlineStr">
+      <c r="CL1" t="inlineStr">
         <is>
           <t>returnOnAssets</t>
         </is>
       </c>
-      <c r="CL1" t="inlineStr">
+      <c r="CM1" t="inlineStr">
         <is>
           <t>returnOnEquity</t>
         </is>
       </c>
-      <c r="CM1" t="inlineStr">
+      <c r="CN1" t="inlineStr">
         <is>
           <t>grossProfits</t>
         </is>
       </c>
-      <c r="CN1" t="inlineStr">
+      <c r="CO1" t="inlineStr">
         <is>
           <t>freeCashflow</t>
         </is>
       </c>
-      <c r="CO1" t="inlineStr">
+      <c r="CP1" t="inlineStr">
         <is>
           <t>operatingCashflow</t>
         </is>
       </c>
-      <c r="CP1" t="inlineStr">
+      <c r="CQ1" t="inlineStr">
         <is>
           <t>earningsGrowth</t>
         </is>
       </c>
-      <c r="CQ1" t="inlineStr">
+      <c r="CR1" t="inlineStr">
         <is>
           <t>revenueGrowth</t>
         </is>
       </c>
-      <c r="CR1" t="inlineStr">
+      <c r="CS1" t="inlineStr">
         <is>
           <t>grossMargins</t>
         </is>
       </c>
-      <c r="CS1" t="inlineStr">
+      <c r="CT1" t="inlineStr">
         <is>
           <t>ebitdaMargins</t>
         </is>
       </c>
-      <c r="CT1" t="inlineStr">
+      <c r="CU1" t="inlineStr">
         <is>
           <t>operatingMargins</t>
         </is>
       </c>
-      <c r="CU1" t="inlineStr">
+      <c r="CV1" t="inlineStr">
         <is>
           <t>financialCurrency</t>
         </is>
       </c>
-      <c r="CV1" t="inlineStr">
+      <c r="CW1" t="inlineStr">
         <is>
           <t>symbol</t>
         </is>
       </c>
-      <c r="CW1" t="inlineStr">
+      <c r="CX1" t="inlineStr">
         <is>
           <t>language</t>
         </is>
       </c>
-      <c r="CX1" t="inlineStr">
+      <c r="CY1" t="inlineStr">
         <is>
           <t>region</t>
         </is>
       </c>
-      <c r="CY1" t="inlineStr">
+      <c r="CZ1" t="inlineStr">
         <is>
           <t>typeDisp</t>
         </is>
       </c>
-      <c r="CZ1" t="inlineStr">
+      <c r="DA1" t="inlineStr">
         <is>
           <t>quoteSourceName</t>
         </is>
       </c>
-      <c r="DA1" t="inlineStr">
+      <c r="DB1" t="inlineStr">
         <is>
           <t>triggerable</t>
         </is>
       </c>
-      <c r="DB1" t="inlineStr">
+      <c r="DC1" t="inlineStr">
         <is>
           <t>customPriceAlertConfidence</t>
         </is>
       </c>
-      <c r="DC1" t="inlineStr">
+      <c r="DD1" t="inlineStr">
+        <is>
+          <t>corporateActions</t>
+        </is>
+      </c>
+      <c r="DE1" t="inlineStr">
+        <is>
+          <t>regularMarketTime</t>
+        </is>
+      </c>
+      <c r="DF1" t="inlineStr">
+        <is>
+          <t>exchange</t>
+        </is>
+      </c>
+      <c r="DG1" t="inlineStr">
+        <is>
+          <t>messageBoardId</t>
+        </is>
+      </c>
+      <c r="DH1" t="inlineStr">
+        <is>
+          <t>exchangeTimezoneName</t>
+        </is>
+      </c>
+      <c r="DI1" t="inlineStr">
+        <is>
+          <t>exchangeTimezoneShortName</t>
+        </is>
+      </c>
+      <c r="DJ1" t="inlineStr">
+        <is>
+          <t>gmtOffSetMilliseconds</t>
+        </is>
+      </c>
+      <c r="DK1" t="inlineStr">
+        <is>
+          <t>market</t>
+        </is>
+      </c>
+      <c r="DL1" t="inlineStr">
+        <is>
+          <t>esgPopulated</t>
+        </is>
+      </c>
+      <c r="DM1" t="inlineStr">
+        <is>
+          <t>regularMarketChangePercent</t>
+        </is>
+      </c>
+      <c r="DN1" t="inlineStr">
+        <is>
+          <t>regularMarketPrice</t>
+        </is>
+      </c>
+      <c r="DO1" t="inlineStr">
+        <is>
+          <t>longName</t>
+        </is>
+      </c>
+      <c r="DP1" t="inlineStr">
+        <is>
+          <t>hasPrePostMarketData</t>
+        </is>
+      </c>
+      <c r="DQ1" t="inlineStr">
+        <is>
+          <t>firstTradeDateMilliseconds</t>
+        </is>
+      </c>
+      <c r="DR1" t="inlineStr">
+        <is>
+          <t>regularMarketChange</t>
+        </is>
+      </c>
+      <c r="DS1" t="inlineStr">
+        <is>
+          <t>regularMarketDayRange</t>
+        </is>
+      </c>
+      <c r="DT1" t="inlineStr">
+        <is>
+          <t>fullExchangeName</t>
+        </is>
+      </c>
+      <c r="DU1" t="inlineStr">
+        <is>
+          <t>averageDailyVolume3Month</t>
+        </is>
+      </c>
+      <c r="DV1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekLowChange</t>
+        </is>
+      </c>
+      <c r="DW1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekLowChangePercent</t>
+        </is>
+      </c>
+      <c r="DX1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekRange</t>
+        </is>
+      </c>
+      <c r="DY1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekHighChange</t>
+        </is>
+      </c>
+      <c r="DZ1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekHighChangePercent</t>
+        </is>
+      </c>
+      <c r="EA1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekChangePercent</t>
+        </is>
+      </c>
+      <c r="EB1" t="inlineStr">
+        <is>
+          <t>earningsTimestampStart</t>
+        </is>
+      </c>
+      <c r="EC1" t="inlineStr">
+        <is>
+          <t>earningsTimestampEnd</t>
+        </is>
+      </c>
+      <c r="ED1" t="inlineStr">
+        <is>
+          <t>epsTrailingTwelveMonths</t>
+        </is>
+      </c>
+      <c r="EE1" t="inlineStr">
+        <is>
+          <t>fiftyDayAverageChange</t>
+        </is>
+      </c>
+      <c r="EF1" t="inlineStr">
+        <is>
+          <t>fiftyDayAverageChangePercent</t>
+        </is>
+      </c>
+      <c r="EG1" t="inlineStr">
+        <is>
+          <t>twoHundredDayAverageChange</t>
+        </is>
+      </c>
+      <c r="EH1" t="inlineStr">
+        <is>
+          <t>twoHundredDayAverageChangePercent</t>
+        </is>
+      </c>
+      <c r="EI1" t="inlineStr">
+        <is>
+          <t>sourceInterval</t>
+        </is>
+      </c>
+      <c r="EJ1" t="inlineStr">
+        <is>
+          <t>exchangeDataDelayedBy</t>
+        </is>
+      </c>
+      <c r="EK1" t="inlineStr">
+        <is>
+          <t>cryptoTradeable</t>
+        </is>
+      </c>
+      <c r="EL1" t="inlineStr">
+        <is>
+          <t>marketState</t>
+        </is>
+      </c>
+      <c r="EM1" t="inlineStr">
         <is>
           <t>shortName</t>
         </is>
       </c>
-      <c r="DD1" t="inlineStr">
-        <is>
-          <t>longName</t>
-        </is>
-      </c>
-      <c r="DE1" t="inlineStr">
-        <is>
-          <t>corporateActions</t>
-        </is>
-      </c>
-      <c r="DF1" t="inlineStr">
-        <is>
-          <t>regularMarketTime</t>
-        </is>
-      </c>
-      <c r="DG1" t="inlineStr">
-        <is>
-          <t>exchange</t>
-        </is>
-      </c>
-      <c r="DH1" t="inlineStr">
-        <is>
-          <t>messageBoardId</t>
-        </is>
-      </c>
-      <c r="DI1" t="inlineStr">
-        <is>
-          <t>exchangeTimezoneName</t>
-        </is>
-      </c>
-      <c r="DJ1" t="inlineStr">
-        <is>
-          <t>exchangeTimezoneShortName</t>
-        </is>
-      </c>
-      <c r="DK1" t="inlineStr">
-        <is>
-          <t>gmtOffSetMilliseconds</t>
-        </is>
-      </c>
-      <c r="DL1" t="inlineStr">
-        <is>
-          <t>market</t>
-        </is>
-      </c>
-      <c r="DM1" t="inlineStr">
-        <is>
-          <t>esgPopulated</t>
-        </is>
-      </c>
-      <c r="DN1" t="inlineStr">
-        <is>
-          <t>regularMarketChangePercent</t>
-        </is>
-      </c>
-      <c r="DO1" t="inlineStr">
-        <is>
-          <t>regularMarketPrice</t>
-        </is>
-      </c>
-      <c r="DP1" t="inlineStr">
-        <is>
-          <t>marketState</t>
-        </is>
-      </c>
-      <c r="DQ1" t="inlineStr">
-        <is>
-          <t>sourceInterval</t>
-        </is>
-      </c>
-      <c r="DR1" t="inlineStr">
-        <is>
-          <t>exchangeDataDelayedBy</t>
-        </is>
-      </c>
-      <c r="DS1" t="inlineStr">
-        <is>
-          <t>cryptoTradeable</t>
-        </is>
-      </c>
-      <c r="DT1" t="inlineStr">
-        <is>
-          <t>hasPrePostMarketData</t>
-        </is>
-      </c>
-      <c r="DU1" t="inlineStr">
-        <is>
-          <t>firstTradeDateMilliseconds</t>
-        </is>
-      </c>
-      <c r="DV1" t="inlineStr">
-        <is>
-          <t>regularMarketChange</t>
-        </is>
-      </c>
-      <c r="DW1" t="inlineStr">
-        <is>
-          <t>regularMarketDayRange</t>
-        </is>
-      </c>
-      <c r="DX1" t="inlineStr">
-        <is>
-          <t>fullExchangeName</t>
-        </is>
-      </c>
-      <c r="DY1" t="inlineStr">
-        <is>
-          <t>averageDailyVolume3Month</t>
-        </is>
-      </c>
-      <c r="DZ1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekLowChange</t>
-        </is>
-      </c>
-      <c r="EA1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekLowChangePercent</t>
-        </is>
-      </c>
-      <c r="EB1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekRange</t>
-        </is>
-      </c>
-      <c r="EC1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekHighChange</t>
-        </is>
-      </c>
-      <c r="ED1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekHighChangePercent</t>
-        </is>
-      </c>
-      <c r="EE1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekChangePercent</t>
-        </is>
-      </c>
-      <c r="EF1" t="inlineStr">
-        <is>
-          <t>earningsTimestampStart</t>
-        </is>
-      </c>
-      <c r="EG1" t="inlineStr">
-        <is>
-          <t>earningsTimestampEnd</t>
-        </is>
-      </c>
-      <c r="EH1" t="inlineStr">
-        <is>
-          <t>epsTrailingTwelveMonths</t>
-        </is>
-      </c>
-      <c r="EI1" t="inlineStr">
-        <is>
-          <t>fiftyDayAverageChange</t>
-        </is>
-      </c>
-      <c r="EJ1" t="inlineStr">
-        <is>
-          <t>fiftyDayAverageChangePercent</t>
-        </is>
-      </c>
-      <c r="EK1" t="inlineStr">
-        <is>
-          <t>twoHundredDayAverageChange</t>
-        </is>
-      </c>
-      <c r="EL1" t="inlineStr">
-        <is>
-          <t>twoHundredDayAverageChangePercent</t>
-        </is>
-      </c>
-      <c r="EM1" t="inlineStr">
+      <c r="EN1" t="inlineStr">
         <is>
           <t>trailingPegRatio</t>
         </is>
@@ -4241,487 +4246,492 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>86 576 8595 6088</t>
+          <t>86 57 68595 6088</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
+          <t>86 57 6859 56299</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
           <t>https://www.yotrio.com</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="H2" t="inlineStr">
         <is>
           <t>Furnishings, Fixtures &amp; Appliances</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="I2" t="inlineStr">
         <is>
           <t>furnishings-fixtures-appliances</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
+      <c r="J2" t="inlineStr">
         <is>
           <t>Furnishings, Fixtures &amp; Appliances</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="K2" t="inlineStr">
         <is>
           <t>Consumer Cyclical</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="L2" t="inlineStr">
         <is>
           <t>consumer-cyclical</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t>Consumer Cyclical</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>Yotrio Group Co., Ltd. manufactures, and sells outdoor furniture products in China, Europe, North and South America, Australia, Asia, Africa, and internationally. The company's product portfolio includes aluminum and steel products, meshes, wickers, resin wood and wood products, slings, creatop table tops, and glass table tops. Yotrio Group Co., Ltd. was founded in 1992 and is based in Linhai, China.</t>
-        </is>
-      </c>
-      <c r="N2" t="n">
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>Yotrio Group Co., Ltd. engages in the manufacture and sale of outdoor products and furniture in China, Europe, North and South America, Australia, the rest of Asia, and Africa. It offers outdoor leisure furniture, parasols, tents, and peripheral products; patio tables and chairs, parasols, tents, outdoor barbecue and picnic equipment, camping gear, garden tool sheds, and garden fences. The company was founded in 1992 and is based in Linhai, China.</t>
+        </is>
+      </c>
+      <c r="O2" t="n">
         <v>10505</v>
       </c>
-      <c r="O2" t="inlineStr">
+      <c r="P2" t="inlineStr">
         <is>
           <t>[{'maxAge': 1, 'name': 'Mr. Jian Qiang  Xie', 'age': 50, 'title': 'GM &amp; Vice Chairman', 'yearBorn': 1975, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Fu Bin  Shi', 'age': 53, 'title': 'CFO, Executive Deputy GM &amp; Director', 'yearBorn': 1972, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Hong Yang  Wang', 'age': 48, 'title': 'Deputy GM &amp; Secretary of Board', 'yearBorn': 1977, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Huhua  Zhou', 'age': 50, 'title': 'Deputy General Manager', 'yearBorn': 1975, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Qiong  Hu', 'title': 'Accounting Supervisor', 'exercisedValue': 0, 'unexercisedValue': 0}]</t>
         </is>
       </c>
-      <c r="P2" t="inlineStr">
+      <c r="Q2" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="Q2" t="n">
+      <c r="R2" t="n">
         <v>86400</v>
       </c>
-      <c r="R2" t="n">
+      <c r="S2" t="n">
         <v>4</v>
       </c>
-      <c r="S2" t="n">
-        <v>3.04</v>
-      </c>
       <c r="T2" t="n">
-        <v>3.18</v>
+        <v>2.79</v>
       </c>
       <c r="U2" t="n">
-        <v>2.88</v>
+        <v>2.79</v>
       </c>
       <c r="V2" t="n">
-        <v>3.02</v>
+        <v>2.79</v>
       </c>
       <c r="W2" t="n">
-        <v>3.04</v>
+        <v>2.86</v>
       </c>
       <c r="X2" t="n">
-        <v>3.18</v>
+        <v>2.79</v>
       </c>
       <c r="Y2" t="n">
-        <v>2.88</v>
+        <v>2.79</v>
       </c>
       <c r="Z2" t="n">
-        <v>3.02</v>
+        <v>2.79</v>
       </c>
       <c r="AA2" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="AB2" t="n">
         <v>0.06</v>
       </c>
-      <c r="AB2" t="n">
-        <v>2.04</v>
-      </c>
       <c r="AC2" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AD2" t="n">
         <v>1780444800</v>
       </c>
-      <c r="AD2" t="n">
+      <c r="AE2" t="n">
         <v>0.36360002</v>
       </c>
-      <c r="AE2" t="n">
-        <v>1.39</v>
-      </c>
       <c r="AF2" t="n">
-        <v>0.284</v>
+        <v>1.36</v>
       </c>
       <c r="AG2" t="n">
-        <v>26.727274</v>
+        <v>0.319</v>
       </c>
       <c r="AH2" t="n">
-        <v>43174804</v>
+        <v>25.818182</v>
       </c>
       <c r="AI2" t="n">
-        <v>43174804</v>
+        <v>24404264</v>
       </c>
       <c r="AJ2" t="n">
-        <v>47347494</v>
+        <v>24404264</v>
       </c>
       <c r="AK2" t="n">
-        <v>44316343</v>
+        <v>49003694</v>
       </c>
       <c r="AL2" t="n">
-        <v>44316343</v>
+        <v>31880995</v>
       </c>
       <c r="AM2" t="n">
-        <v>2.94</v>
+        <v>31880995</v>
       </c>
       <c r="AN2" t="n">
-        <v>2.95</v>
+        <v>2.84</v>
       </c>
       <c r="AO2" t="n">
-        <v>6376908288</v>
+        <v>2.85</v>
       </c>
       <c r="AP2" t="n">
-        <v>6593809591</v>
+        <v>6160006144</v>
       </c>
       <c r="AQ2" t="n">
-        <v>2.88</v>
+        <v>6008175187</v>
       </c>
       <c r="AR2" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="AS2" t="n">
         <v>4.21</v>
       </c>
-      <c r="AS2" t="n">
+      <c r="AT2" t="n">
         <v>14.851428</v>
       </c>
-      <c r="AT2" t="n">
+      <c r="AU2" t="n">
         <v>0.025094</v>
       </c>
-      <c r="AU2" t="n">
-        <v>1.1417625</v>
-      </c>
       <c r="AV2" t="n">
-        <v>3.5652</v>
+        <v>1.102927</v>
       </c>
       <c r="AW2" t="n">
-        <v>3.70415</v>
+        <v>3.457</v>
       </c>
       <c r="AX2" t="n">
+        <v>3.6566</v>
+      </c>
+      <c r="AY2" t="n">
         <v>0.06</v>
       </c>
-      <c r="AY2" t="n">
-        <v>0.019736841</v>
-      </c>
-      <c r="AZ2" t="inlineStr">
+      <c r="AZ2" t="n">
+        <v>0.021505376</v>
+      </c>
+      <c r="BA2" t="inlineStr">
         <is>
           <t>CNY</t>
         </is>
       </c>
-      <c r="BA2" t="b">
+      <c r="BB2" t="b">
         <v>0</v>
       </c>
-      <c r="BB2" t="n">
-        <v>5395500544</v>
-      </c>
       <c r="BC2" t="n">
+        <v>5178598912</v>
+      </c>
+      <c r="BD2" t="n">
         <v>0.044499997</v>
       </c>
-      <c r="BD2" t="n">
+      <c r="BE2" t="n">
         <v>1015316536</v>
       </c>
-      <c r="BE2" t="n">
+      <c r="BF2" t="n">
         <v>2169016313</v>
       </c>
-      <c r="BF2" t="n">
+      <c r="BG2" t="n">
         <v>0.54644</v>
       </c>
-      <c r="BG2" t="n">
-        <v>0.0216</v>
-      </c>
       <c r="BH2" t="n">
+        <v>0.02161</v>
+      </c>
+      <c r="BI2" t="n">
         <v>2169016313</v>
       </c>
-      <c r="BI2" t="n">
+      <c r="BJ2" t="n">
         <v>2.119</v>
       </c>
-      <c r="BJ2" t="n">
-        <v>1.387447</v>
-      </c>
       <c r="BK2" t="n">
+        <v>1.3402548</v>
+      </c>
+      <c r="BL2" t="n">
         <v>1767139200</v>
       </c>
-      <c r="BL2" t="n">
+      <c r="BM2" t="n">
         <v>1798675200</v>
       </c>
-      <c r="BM2" t="n">
+      <c r="BN2" t="n">
         <v>1774915200</v>
       </c>
-      <c r="BN2" t="n">
+      <c r="BO2" t="n">
         <v>-0.583</v>
       </c>
-      <c r="BO2" t="n">
+      <c r="BP2" t="n">
         <v>248549104</v>
       </c>
-      <c r="BP2" t="n">
+      <c r="BQ2" t="n">
         <v>0.11</v>
       </c>
-      <c r="BQ2" t="inlineStr">
+      <c r="BR2" t="inlineStr">
         <is>
           <t>35:10</t>
         </is>
       </c>
-      <c r="BR2" t="n">
+      <c r="BS2" t="n">
         <v>1443052800</v>
       </c>
-      <c r="BS2" t="n">
-        <v>0.966</v>
-      </c>
       <c r="BT2" t="n">
-        <v>23.089</v>
+        <v>0.927</v>
       </c>
       <c r="BU2" t="n">
-        <v>-0.14606744</v>
+        <v>22.161</v>
       </c>
       <c r="BV2" t="n">
-        <v>0.24487448</v>
+        <v>-0.23770493</v>
       </c>
       <c r="BW2" t="n">
+        <v>0.20116603</v>
+      </c>
+      <c r="BX2" t="n">
         <v>0.06</v>
       </c>
-      <c r="BX2" t="n">
+      <c r="BY2" t="n">
         <v>1780444800</v>
       </c>
-      <c r="BY2" t="inlineStr">
+      <c r="BZ2" t="inlineStr">
         <is>
           <t>EQUITY</t>
         </is>
       </c>
-      <c r="BZ2" t="n">
-        <v>2.94</v>
-      </c>
-      <c r="CA2" t="inlineStr">
+      <c r="CA2" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="CB2" t="inlineStr">
         <is>
           <t>none</t>
         </is>
       </c>
-      <c r="CB2" t="n">
+      <c r="CC2" t="n">
         <v>2285286912</v>
       </c>
-      <c r="CC2" t="n">
+      <c r="CD2" t="n">
         <v>1.054</v>
       </c>
-      <c r="CD2" t="n">
+      <c r="CE2" t="n">
         <v>233684672</v>
       </c>
-      <c r="CE2" t="n">
+      <c r="CF2" t="n">
         <v>1294675584</v>
       </c>
-      <c r="CF2" t="n">
+      <c r="CG2" t="n">
         <v>1.306</v>
       </c>
-      <c r="CG2" t="n">
+      <c r="CH2" t="n">
         <v>1.553</v>
       </c>
-      <c r="CH2" t="n">
+      <c r="CI2" t="n">
         <v>5585144320</v>
       </c>
-      <c r="CI2" t="n">
+      <c r="CJ2" t="n">
         <v>28.118</v>
       </c>
-      <c r="CJ2" t="n">
+      <c r="CK2" t="n">
         <v>2.567</v>
       </c>
-      <c r="CK2" t="n">
+      <c r="CL2" t="n">
         <v>0.010240001</v>
       </c>
-      <c r="CL2" t="n">
+      <c r="CM2" t="n">
         <v>0.056560002</v>
       </c>
-      <c r="CM2" t="n">
+      <c r="CN2" t="n">
         <v>983623808</v>
       </c>
-      <c r="CN2" t="n">
+      <c r="CO2" t="n">
         <v>-354109120</v>
       </c>
-      <c r="CO2" t="n">
+      <c r="CP2" t="n">
         <v>-61140864</v>
       </c>
-      <c r="CP2" t="n">
+      <c r="CQ2" t="n">
         <v>-0.588</v>
       </c>
-      <c r="CQ2" t="n">
+      <c r="CR2" t="n">
         <v>-0.029</v>
       </c>
-      <c r="CR2" t="n">
+      <c r="CS2" t="n">
         <v>0.17611</v>
       </c>
-      <c r="CS2" t="n">
+      <c r="CT2" t="n">
         <v>0.041840002</v>
       </c>
-      <c r="CT2" t="n">
+      <c r="CU2" t="n">
         <v>0.11611</v>
       </c>
-      <c r="CU2" t="inlineStr">
+      <c r="CV2" t="inlineStr">
         <is>
           <t>CNY</t>
         </is>
       </c>
-      <c r="CV2" t="inlineStr">
+      <c r="CW2" t="inlineStr">
         <is>
           <t>002489.SZ</t>
         </is>
       </c>
-      <c r="CW2" t="inlineStr">
+      <c r="CX2" t="inlineStr">
         <is>
           <t>en-US</t>
         </is>
       </c>
-      <c r="CX2" t="inlineStr">
+      <c r="CY2" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="CY2" t="inlineStr">
+      <c r="CZ2" t="inlineStr">
         <is>
           <t>Equity</t>
         </is>
       </c>
-      <c r="CZ2" t="inlineStr">
+      <c r="DA2" t="inlineStr">
         <is>
           <t>Delayed Quote</t>
         </is>
       </c>
-      <c r="DA2" t="b">
+      <c r="DB2" t="b">
         <v>0</v>
       </c>
-      <c r="DB2" t="inlineStr">
+      <c r="DC2" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="DC2" t="inlineStr">
+      <c r="DD2" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="DE2" t="n">
+        <v>1783062240</v>
+      </c>
+      <c r="DF2" t="inlineStr">
+        <is>
+          <t>SHZ</t>
+        </is>
+      </c>
+      <c r="DG2" t="inlineStr">
+        <is>
+          <t>finmb_59263363</t>
+        </is>
+      </c>
+      <c r="DH2" t="inlineStr">
+        <is>
+          <t>Asia/Shanghai</t>
+        </is>
+      </c>
+      <c r="DI2" t="inlineStr">
+        <is>
+          <t>CST</t>
+        </is>
+      </c>
+      <c r="DJ2" t="n">
+        <v>28800000</v>
+      </c>
+      <c r="DK2" t="inlineStr">
+        <is>
+          <t>cn_market</t>
+        </is>
+      </c>
+      <c r="DL2" t="b">
+        <v>0</v>
+      </c>
+      <c r="DM2" t="n">
+        <v>1.792113</v>
+      </c>
+      <c r="DN2" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="DO2" t="inlineStr">
+        <is>
+          <t>Yotrio Group Co., Ltd.</t>
+        </is>
+      </c>
+      <c r="DP2" t="b">
+        <v>0</v>
+      </c>
+      <c r="DQ2" t="n">
+        <v>1283995800000</v>
+      </c>
+      <c r="DR2" t="n">
+        <v>0.049999952</v>
+      </c>
+      <c r="DS2" t="inlineStr">
+        <is>
+          <t>2.79 - 2.86</t>
+        </is>
+      </c>
+      <c r="DT2" t="inlineStr">
+        <is>
+          <t>Shenzhen</t>
+        </is>
+      </c>
+      <c r="DU2" t="n">
+        <v>49003694</v>
+      </c>
+      <c r="DV2" t="n">
+        <v>0.19999981</v>
+      </c>
+      <c r="DW2" t="n">
+        <v>0.07575750000000001</v>
+      </c>
+      <c r="DX2" t="inlineStr">
+        <is>
+          <t>2.64 - 4.21</t>
+        </is>
+      </c>
+      <c r="DY2" t="n">
+        <v>-1.3700001</v>
+      </c>
+      <c r="DZ2" t="n">
+        <v>-0.3254157</v>
+      </c>
+      <c r="EA2" t="n">
+        <v>-23.770493</v>
+      </c>
+      <c r="EB2" t="n">
+        <v>1651229940</v>
+      </c>
+      <c r="EC2" t="n">
+        <v>1651492800</v>
+      </c>
+      <c r="ED2" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="EE2" t="n">
+        <v>-0.6170001000000001</v>
+      </c>
+      <c r="EF2" t="n">
+        <v>-0.17847848</v>
+      </c>
+      <c r="EG2" t="n">
+        <v>-0.8166001000000001</v>
+      </c>
+      <c r="EH2" t="n">
+        <v>-0.22332223</v>
+      </c>
+      <c r="EI2" t="n">
+        <v>15</v>
+      </c>
+      <c r="EJ2" t="n">
+        <v>15</v>
+      </c>
+      <c r="EK2" t="b">
+        <v>0</v>
+      </c>
+      <c r="EL2" t="inlineStr">
+        <is>
+          <t>CLOSED</t>
+        </is>
+      </c>
+      <c r="EM2" t="inlineStr">
         <is>
           <t>YOTRIO GROUP CO LTD</t>
         </is>
       </c>
-      <c r="DD2" t="inlineStr">
-        <is>
-          <t>Yotrio Group Co., Ltd.</t>
-        </is>
-      </c>
-      <c r="DE2" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="DF2" t="n">
-        <v>1782111876</v>
-      </c>
-      <c r="DG2" t="inlineStr">
-        <is>
-          <t>SHZ</t>
-        </is>
-      </c>
-      <c r="DH2" t="inlineStr">
-        <is>
-          <t>finmb_59263363</t>
-        </is>
-      </c>
-      <c r="DI2" t="inlineStr">
-        <is>
-          <t>Asia/Shanghai</t>
-        </is>
-      </c>
-      <c r="DJ2" t="inlineStr">
-        <is>
-          <t>CST</t>
-        </is>
-      </c>
-      <c r="DK2" t="n">
-        <v>28800000</v>
-      </c>
-      <c r="DL2" t="inlineStr">
-        <is>
-          <t>cn_market</t>
-        </is>
-      </c>
-      <c r="DM2" t="b">
-        <v>0</v>
-      </c>
-      <c r="DN2" t="n">
-        <v>-3.2894704</v>
-      </c>
-      <c r="DO2" t="n">
-        <v>2.94</v>
-      </c>
-      <c r="DP2" t="inlineStr">
-        <is>
-          <t>PREPRE</t>
-        </is>
-      </c>
-      <c r="DQ2" t="n">
-        <v>15</v>
-      </c>
-      <c r="DR2" t="n">
-        <v>15</v>
-      </c>
-      <c r="DS2" t="b">
-        <v>0</v>
-      </c>
-      <c r="DT2" t="b">
-        <v>0</v>
-      </c>
-      <c r="DU2" t="n">
-        <v>1283995800000</v>
-      </c>
-      <c r="DV2" t="n">
-        <v>-0.099999905</v>
-      </c>
-      <c r="DW2" t="inlineStr">
-        <is>
-          <t>2.88 - 3.02</t>
-        </is>
-      </c>
-      <c r="DX2" t="inlineStr">
-        <is>
-          <t>Shenzhen</t>
-        </is>
-      </c>
-      <c r="DY2" t="n">
-        <v>47347494</v>
-      </c>
-      <c r="DZ2" t="n">
-        <v>0.059999943</v>
-      </c>
-      <c r="EA2" t="n">
-        <v>0.020833313</v>
-      </c>
-      <c r="EB2" t="inlineStr">
-        <is>
-          <t>2.88 - 4.21</t>
-        </is>
-      </c>
-      <c r="EC2" t="n">
-        <v>-1.27</v>
-      </c>
-      <c r="ED2" t="n">
-        <v>-0.3016627</v>
-      </c>
-      <c r="EE2" t="n">
-        <v>-14.606744</v>
-      </c>
-      <c r="EF2" t="n">
-        <v>1651229940</v>
-      </c>
-      <c r="EG2" t="n">
-        <v>1651492800</v>
-      </c>
-      <c r="EH2" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="EI2" t="n">
-        <v>-0.62520003</v>
-      </c>
-      <c r="EJ2" t="n">
-        <v>-0.17536184</v>
-      </c>
-      <c r="EK2" t="n">
-        <v>-0.7641499</v>
-      </c>
-      <c r="EL2" t="n">
-        <v>-0.20629562</v>
-      </c>
-      <c r="EM2" t="inlineStr"/>
+      <c r="EN2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
